--- a/thesis_docs/exhibits/ch03_methodology/workbooks/01_Sample_and_Airport_Selection.xlsx
+++ b/thesis_docs/exhibits/ch03_methodology/workbooks/01_Sample_and_Airport_Selection.xlsx
@@ -546,7 +546,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="31" customWidth="1" min="2" max="2"/>
@@ -869,7 +869,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
@@ -1084,7 +1084,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
@@ -1246,7 +1246,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
@@ -1554,7 +1554,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
@@ -1738,7 +1738,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
@@ -1944,7 +1944,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
@@ -2114,7 +2114,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="56" customWidth="1" min="2" max="2"/>

--- a/thesis_docs/exhibits/ch03_methodology/workbooks/01_Sample_and_Airport_Selection.xlsx
+++ b/thesis_docs/exhibits/ch03_methodology/workbooks/01_Sample_and_Airport_Selection.xlsx
@@ -13,8 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="connecting_paradox" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="data_sample_profile" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="top25_network_approach" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="post_pandemic_justification" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="power_of_9_airports" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="power_of_9_airports" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -545,11 +544,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
@@ -771,71 +770,39 @@
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Table 1.6</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>post_pandemic_justification</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Post-Pandemic Temporal Demarcation Evaluation (Candidate A vs. Candidate B)</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>Comparative evaluation of Candidate A (Mature) vs Candidate B (May 1, 2022 Boundary)</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>6 rows x 3 cols</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>Temporal Demarcation</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>Table 1.7</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>power_of_9_airports</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>The Nine-Airport Experimental Cohort: Generalizability and Twin Disruption Controls</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>Spatial transfer pairs, twin disruption shock absorber controls, and statistical balance</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>5 rows x 5 cols</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>Experimental Cohort Design</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="14" t="inlineStr">
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>Note. Master consolidated tabular dataset corresponding to figures in 01_Sample_and_Airport_Selection. Formatted strictly according to APA Style (7th ed.) with horizontal boundary rules, zero auto-filters, and no background shading.</t>
         </is>
@@ -855,8 +822,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1943,176 +1908,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
-        <is>
-          <t>⬅ Return to Table of Contents</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
-        <is>
-          <t>Table 1.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="17" t="inlineStr">
-        <is>
-          <t>Post-Pandemic Temporal Demarcation Evaluation (Candidate A vs. Candidate B)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="10" customHeight="1"/>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Demarcation Evaluation Dimension</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Candidate A: Mature Post-Pandemic (Jan 2023)</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Candidate B: Early Post-Mask Regime (May 2022; Selected)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>Start Date</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>January 1, 2023</t>
-        </is>
-      </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>May 1, 2022</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
-        <is>
-          <t>Statistical Rationale</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>Full seasonal convergence (p &gt;= 0.05 on rolling Welch's t-test) and net cumulative passenger deficit reached minimum.</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>CUSUM stabilization, Chow test parameter stability, and removal of federal transit mask mandates.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
-        <is>
-          <t>Data Volume for Training</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>~24 months training (2023-01-01 to 2024-12-31) and 12 months test (2025).</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>36 months training/val (2022-05-01 to 2024-12-31) and 12 months test (2025).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="18" t="inlineStr">
-        <is>
-          <t>Impact on Robustness</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>Excellent; zero contamination from 2022 recovery fluctuations.</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>Superior; provides 2 full annual seasonal cycles in training, enabling ML/Probabilistic models to learn holiday and summer peaks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
-        <is>
-          <t>Impact on Resilience</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>Moderate; misses the December 2022 Winter Storm Elliott mega-disruption, which is the prime real-world shock event.</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>Superior; captures December 2022 and Summer 2023 convective storms, allowing direct computation of TTR and R_MASE.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="22" t="inlineStr">
-        <is>
-          <t>Impact on Generalizability</t>
-        </is>
-      </c>
-      <c r="B11" s="22" t="inlineStr">
-        <is>
-          <t>Adequate, but smaller sample sizes for regional/spoke airport cohorts.</t>
-        </is>
-      </c>
-      <c r="C11" s="22" t="inlineStr">
-        <is>
-          <t>Superior; includes 404k+ hourly observations across all 25 airfields, maximizing spatial transferability tests.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="21" t="inlineStr">
-        <is>
-          <t>Note. Comparative evaluation of post-pandemic temporal demarcation regimes. Candidate B (May 1, 2022 to December 31, 2025; 44 months) was formally selected for maximum statistical power while preserving structural regime stability.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2133,7 +1928,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>Table 1.7</t>
+          <t>Table 1.6</t>
         </is>
       </c>
     </row>

--- a/thesis_docs/exhibits/ch03_methodology/workbooks/01_Sample_and_Airport_Selection.xlsx
+++ b/thesis_docs/exhibits/ch03_methodology/workbooks/01_Sample_and_Airport_Selection.xlsx
@@ -56,9 +56,8 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <b val="1"/>
       <color rgb="000563C1"/>
-      <sz val="10"/>
+      <sz val="11"/>
       <u val="single"/>
     </font>
     <font>
